--- a/task_submission/4.1_内存自验证报告.xlsx
+++ b/task_submission/4.1_内存自验证报告.xlsx
@@ -57,7 +57,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -71,11 +71,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +117,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +517,7 @@
           <t>TurboQuantAttentionScore</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
+      <c r="C2" s="5" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>硬件型号</t>
@@ -498,7 +528,7 @@
           <t>Ascend 910B3（Atlas 800T A2）</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
+      <c r="F2" s="5" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>CANN版本</t>
@@ -509,8 +539,8 @@
           <t>9.1.0</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
+      <c r="I2" s="6" t="n"/>
+      <c r="J2" s="5" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -523,7 +553,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n"/>
+      <c r="C3" s="5" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>代码提交</t>
@@ -531,10 +561,10 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>96818d4f</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="n"/>
+          <t>72bb444f</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Golden</t>
@@ -545,8 +575,8 @@
           <t>CPU 参考（与 tests/pytest/golden.py 同公式；本算子无 TBE）</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="5" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -652,28 +682,29 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>任务书 §3.4 内存要求：不涉及。本表仅作占位，验收时以任务书为准。</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E2:F2"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H3:J3"/>

--- a/task_submission/4.1_内存自验证报告.xlsx
+++ b/task_submission/4.1_内存自验证报告.xlsx
@@ -26,21 +26,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
+      <name val="宋体"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -57,7 +57,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,39 +71,11 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -117,8 +89,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,19 +455,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="52" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -517,7 +488,7 @@
           <t>TurboQuantAttentionScore</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>硬件型号</t>
@@ -528,7 +499,7 @@
           <t>Ascend 910B3（Atlas 800T A2）</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>CANN版本</t>
@@ -539,8 +510,8 @@
           <t>9.1.0</t>
         </is>
       </c>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="5" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -553,7 +524,7 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>代码提交</t>
@@ -561,10 +532,10 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>72bb444f</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="n"/>
+          <t>9c168855</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Golden</t>
@@ -572,13 +543,13 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>CPU 参考（与 tests/pytest/golden.py 同公式；本算子无 TBE）</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="n"/>
-      <c r="J3" s="5" t="n"/>
+          <t>CPU 参考（与 golden.py 同公式；本算子无 TBE）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>用例</t>
@@ -611,7 +582,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>TBE算子性能(us)</t>
+          <t>TBE算子性能(us)/Full-QK标杆</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -630,7 +601,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>内存自验证</t>
@@ -673,7 +644,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>本任务书明确「内存要求：不涉及」，不做单独内存验收；运行时输出峰值约 2 GiB（prefill_32k attn_scores）。</t>
+          <t>本任务书明确内存要求不涉及，不做单独内存验收。</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -682,30 +653,53 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="18" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>任务书 §3.4 内存要求：不涉及。本表仅作占位，验收时以任务书为准。</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
+          <t>占位文件。commit 9c168855。</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A7:J9"/>
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="E3:F3"/>
